--- a/49849_Intercuenca_Alto_Huallaga/_raw_reportes_xlsx/IDConfig_64976_completo.xlsx
+++ b/49849_Intercuenca_Alto_Huallaga/_raw_reportes_xlsx/IDConfig_64976_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Rae0579ef38e8465e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Rcebae8a66fde49fe"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,141 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     29.3940</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     29.5998</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     30.2260</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     29.4971</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     29.5398</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     17.6318</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     17.1722</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     17.1296</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     17.8670</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>14/08/2026</x:t>
         </x:is>
       </x:c>
@@ -264,7 +399,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     17.7859</x:v>
+        <x:v>     17.4485</x:v>
       </x:c>
     </x:row>
     <x:row>

--- a/49849_Intercuenca_Alto_Huallaga/_raw_reportes_xlsx/IDConfig_64976_completo.xlsx
+++ b/49849_Intercuenca_Alto_Huallaga/_raw_reportes_xlsx/IDConfig_64976_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Rcebae8a66fde49fe"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Rf1816da207194ecc"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,711 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>10/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     25.0824</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     25.3558</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     25.5949</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     26.3678</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     17.1234</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     16.5990</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     16.4789</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     26.2876</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.3362</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     16.8741</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     20.6604</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     18.4088</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     20.0977</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     19.8582</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.9503</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.5462</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     18.0410</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     17.6156</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     17.4469</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     19.6664</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     23.5559</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     19.3642</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     20.2823</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     20.1894</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     18.1289</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     18.3000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.9145</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     17.9554</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     17.9554</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     17.8699</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     18.0410</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.9897</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.4234</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.3991</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.6181</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     27.5544</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.7663</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     17.9554</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     17.1524</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     15.3689</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     15.5978</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     15.5204</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     15.6752</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     28.2053</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     28.4340</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     16.7886</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     16.7886</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>23/08/2026</x:t>
         </x:is>
       </x:c>
@@ -264,7 +969,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     29.3940</x:v>
+        <x:v>     16.4629</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -279,7 +984,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     29.5998</x:v>
+        <x:v>     16.6246</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -294,7 +999,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     30.2260</x:v>
+        <x:v>     16.5472</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -309,7 +1014,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     29.4971</x:v>
+        <x:v>     16.7886</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -324,7 +1029,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     29.5398</x:v>
+        <x:v>     17.2806</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -339,7 +1044,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     17.6318</x:v>
+        <x:v>     18.3012</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -384,7 +1089,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     17.8670</x:v>
+        <x:v>     17.2584</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -429,7 +1134,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     18.1891</x:v>
+        <x:v>     20.0058</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -444,7 +1149,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     20.1488</x:v>
+        <x:v>     20.1680</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -549,7 +1254,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     17.7338</x:v>
+        <x:v>     17.8550</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1089,7 +1794,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     28.3610</x:v>
+        <x:v>     25.5860</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1104,7 +1809,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     31.5356</x:v>
+        <x:v>     26.2671</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1119,7 +1824,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     30.7572</x:v>
+        <x:v>     25.9290</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1134,7 +1839,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     31.1751</x:v>
+        <x:v>     25.8172</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1149,7 +1854,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     25.5345</x:v>
+        <x:v>     26.0436</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1164,7 +1869,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     26.3389</x:v>
+        <x:v>     26.4934</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1179,7 +1884,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     28.0592</x:v>
+        <x:v>     28.1243</x:v>
       </x:c>
     </x:row>
     <x:row>
